--- a/test-herit-eu/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/test-herit-eu/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-26T14:45:53+00:00</t>
+    <t>2026-03-26T15:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/test-herit-eu/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/test-herit-eu/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-26T15:43:38+00:00</t>
+    <t>2026-03-26T16:51:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
